--- a/plan.xlsx
+++ b/plan.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipi\Downloads\mtg\mtg_clone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FC31857-A8A8-4D70-BE95-EC3199124EB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C6C26CE-D871-4CF4-BEAB-4452E2C739F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4B9AAE7C-4929-4CFC-9ABD-C6251723E409}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -684,6 +685,9 @@
       <c r="C2" t="s">
         <v>12</v>
       </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
       <c r="E2" t="s">
         <v>31</v>
       </c>
@@ -961,4 +965,13 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3089236-C12C-4CAD-B4C4-6F7FBD429364}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/plan.xlsx
+++ b/plan.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipi\Downloads\mtg\mtg_clone\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arjol\Documents\GitHub\mtg_clone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C6C26CE-D871-4CF4-BEAB-4452E2C739F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4B9AAE7C-4929-4CFC-9ABD-C6251723E409}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -273,8 +272,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -649,19 +648,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C0F7F3C-0E7B-406E-9B99-22B8FA879FD3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="40.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.5703125" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.85546875" customWidth="1"/>
-    <col min="5" max="5" width="39.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="40.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.59765625" customWidth="1"/>
+    <col min="3" max="3" width="17.8984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.8984375" customWidth="1"/>
+    <col min="5" max="5" width="39.69921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -675,7 +674,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -691,11 +690,14 @@
       <c r="E2" t="s">
         <v>31</v>
       </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
       <c r="G2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>66</v>
       </c>
@@ -705,14 +707,20 @@
       <c r="C3" t="s">
         <v>13</v>
       </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
       <c r="E3" t="s">
         <v>32</v>
       </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
       <c r="G3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>75</v>
       </c>
@@ -722,6 +730,9 @@
       <c r="C4" t="s">
         <v>14</v>
       </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
       <c r="E4" t="s">
         <v>33</v>
       </c>
@@ -729,7 +740,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -746,7 +757,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -763,7 +774,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -780,7 +791,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -794,7 +805,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -808,7 +819,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>76</v>
       </c>
@@ -822,7 +833,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -836,7 +847,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -850,7 +861,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -861,7 +872,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -872,7 +883,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -883,7 +894,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -894,7 +905,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -905,7 +916,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -916,7 +927,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -927,7 +938,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -938,7 +949,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -949,12 +960,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>51</v>
       </c>
@@ -968,9 +979,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3089236-C12C-4CAD-B4C4-6F7FBD429364}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/plan.xlsx
+++ b/plan.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arjol\Documents\GitHub\mtg_clone\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipi\Downloads\mtg\mtg_clone\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B064B773-1531-48E4-8CE7-E72889B441B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,17 +21,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -68,9 +58,6 @@
     <t>target_card_in_deck</t>
   </si>
   <si>
-    <t>game_mechanic</t>
-  </si>
-  <si>
     <t>trigger_spec</t>
   </si>
   <si>
@@ -267,13 +254,16 @@
   </si>
   <si>
     <t>target_card_in_enemy_hand</t>
+  </si>
+  <si>
+    <t>none</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -648,99 +638,99 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.69921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.59765625" customWidth="1"/>
-    <col min="3" max="3" width="17.8984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.8984375" customWidth="1"/>
-    <col min="5" max="5" width="39.69921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="40.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" customWidth="1"/>
+    <col min="5" max="5" width="39.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="E1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
         <v>12</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
         <v>31</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
         <v>13</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
         <v>32</v>
       </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="G4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -748,16 +738,16 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -765,16 +755,16 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -782,192 +772,192 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
       <c r="C9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" t="s">
         <v>19</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E10" t="s">
         <v>39</v>
       </c>
-      <c r="G9" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" t="s">
-        <v>40</v>
-      </c>
       <c r="G10" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G11" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
-      <c r="A14" t="s">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" t="s">
         <v>24</v>
       </c>
-      <c r="C14" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="E15" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
-      <c r="A15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" t="s">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>25</v>
       </c>
-      <c r="E15" t="s">
+      <c r="C16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
-      <c r="A16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" t="s">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" t="s">
         <v>27</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" t="s">
-        <v>65</v>
-      </c>
-      <c r="E18" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" t="s">
-        <v>69</v>
-      </c>
-      <c r="E19" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" t="s">
+      <c r="C20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>48</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C21" t="s">
         <v>73</v>
       </c>
-      <c r="E20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" t="s">
+      <c r="E21" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>49</v>
       </c>
-      <c r="C21" t="s">
-        <v>74</v>
-      </c>
-      <c r="E21" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" t="s">
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -979,9 +969,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/plan.xlsx
+++ b/plan.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipi\Downloads\mtg\mtg_clone\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arjol\Documents\GitHub\mtg_clone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B064B773-1531-48E4-8CE7-E72889B441B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
   <si>
     <t>target_spec</t>
   </si>
@@ -257,13 +256,19 @@
   </si>
   <si>
     <t>none</t>
+  </si>
+  <si>
+    <t>on_end_phase_on_field</t>
+  </si>
+  <si>
+    <t>on_turn_end_on_field</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -638,19 +643,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="40.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.5703125" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.85546875" customWidth="1"/>
-    <col min="5" max="5" width="39.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="40.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.59765625" customWidth="1"/>
+    <col min="3" max="3" width="20.296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.8984375" customWidth="1"/>
+    <col min="5" max="5" width="39.69921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -664,7 +669,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -687,7 +692,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>65</v>
       </c>
@@ -710,7 +715,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>74</v>
       </c>
@@ -730,7 +735,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -747,7 +752,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -764,7 +769,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -781,7 +786,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -795,7 +800,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -809,7 +814,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>75</v>
       </c>
@@ -823,7 +828,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -837,7 +842,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -851,7 +856,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -862,7 +867,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -873,7 +878,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>76</v>
       </c>
@@ -884,7 +889,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -895,7 +900,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -906,7 +911,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -917,7 +922,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>41</v>
       </c>
@@ -928,7 +933,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -939,7 +944,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -950,14 +955,20 @@
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>50</v>
+      </c>
+      <c r="C23" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -969,9 +980,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/plan.xlsx
+++ b/plan.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
   <si>
     <t>target_spec</t>
   </si>
@@ -262,6 +262,18 @@
   </si>
   <si>
     <t>on_turn_end_on_field</t>
+  </si>
+  <si>
+    <t>when card is attacking</t>
+  </si>
+  <si>
+    <t>when card dies in battle</t>
+  </si>
+  <si>
+    <t>when this card is destroyed from any source</t>
+  </si>
+  <si>
+    <t>When the card destroys another in battle</t>
   </si>
 </sst>
 </file>
@@ -650,7 +662,7 @@
     <col min="1" max="1" width="40.69921875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.59765625" customWidth="1"/>
     <col min="3" max="3" width="20.296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.8984375" customWidth="1"/>
+    <col min="4" max="4" width="36.59765625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="39.69921875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="30.3984375" bestFit="1" customWidth="1"/>
   </cols>
@@ -745,6 +757,9 @@
       <c r="C5" t="s">
         <v>14</v>
       </c>
+      <c r="D5" t="s">
+        <v>79</v>
+      </c>
       <c r="E5" t="s">
         <v>34</v>
       </c>
@@ -762,6 +777,9 @@
       <c r="C6" t="s">
         <v>15</v>
       </c>
+      <c r="D6" t="s">
+        <v>80</v>
+      </c>
       <c r="E6" t="s">
         <v>35</v>
       </c>
@@ -779,6 +797,9 @@
       <c r="C7" t="s">
         <v>16</v>
       </c>
+      <c r="D7" t="s">
+        <v>81</v>
+      </c>
       <c r="E7" t="s">
         <v>36</v>
       </c>
@@ -792,6 +813,9 @@
       </c>
       <c r="C8" t="s">
         <v>17</v>
+      </c>
+      <c r="D8" t="s">
+        <v>82</v>
       </c>
       <c r="E8" t="s">
         <v>37</v>

--- a/plan.xlsx
+++ b/plan.xlsx
@@ -1,24 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arjol\Documents\GitHub\mtg_clone\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipi\Downloads\mtg\mtg_clone\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC79F44-E021-4F7B-9039-53C01DE84AFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="1425" yWindow="1455" windowWidth="11175" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -279,8 +291,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -655,19 +667,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.69921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.59765625" customWidth="1"/>
-    <col min="3" max="3" width="20.296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.69921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="40.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="39.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -681,7 +693,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -704,7 +716,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>65</v>
       </c>
@@ -727,7 +739,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>74</v>
       </c>
@@ -747,7 +759,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -767,7 +779,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -787,7 +799,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -807,7 +819,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -824,7 +836,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -838,7 +850,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>75</v>
       </c>
@@ -852,7 +864,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -866,7 +878,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -880,7 +892,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -891,108 +903,146 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>23</v>
       </c>
       <c r="C14" t="s">
         <v>22</v>
       </c>
+      <c r="D14" t="str">
+        <f>UPPER(C14)&amp;","</f>
+        <v>ON_SUMMON,</v>
+      </c>
       <c r="E14" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>76</v>
       </c>
       <c r="C15" t="s">
         <v>24</v>
       </c>
+      <c r="D15" t="str">
+        <f t="shared" ref="D15:D23" si="0">UPPER(C15)&amp;","</f>
+        <v>ON_MOVE,</v>
+      </c>
       <c r="E15" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>25</v>
       </c>
       <c r="C16" t="s">
         <v>26</v>
       </c>
+      <c r="D16" t="str">
+        <f t="shared" si="0"/>
+        <v>ON_DRAW,</v>
+      </c>
       <c r="E16" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>29</v>
       </c>
       <c r="C17" t="s">
         <v>27</v>
       </c>
+      <c r="D17" t="str">
+        <f t="shared" si="0"/>
+        <v>ON_DEFEND,</v>
+      </c>
       <c r="E17" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>33</v>
       </c>
       <c r="C18" t="s">
         <v>64</v>
       </c>
+      <c r="D18" t="str">
+        <f t="shared" si="0"/>
+        <v>ON_DEATH_ON_FIELD,</v>
+      </c>
       <c r="E18" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>41</v>
       </c>
       <c r="C19" t="s">
         <v>68</v>
       </c>
+      <c r="D19" t="str">
+        <f t="shared" si="0"/>
+        <v>ON_SHIELD_SET,</v>
+      </c>
       <c r="E19" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>47</v>
       </c>
       <c r="C20" t="s">
         <v>72</v>
       </c>
+      <c r="D20" t="str">
+        <f t="shared" si="0"/>
+        <v>ON_EFFECT_DECLARED,</v>
+      </c>
       <c r="E20" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>48</v>
       </c>
       <c r="C21" t="s">
         <v>73</v>
       </c>
+      <c r="D21" t="str">
+        <f t="shared" si="0"/>
+        <v>ON_EFFECT_ACTIVATED,</v>
+      </c>
       <c r="E21" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>49</v>
       </c>
       <c r="C22" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="D22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>50</v>
       </c>
       <c r="C23" t="s">
         <v>78</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1004,9 +1054,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/plan.xlsx
+++ b/plan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipi\Downloads\mtg\mtg_clone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC79F44-E021-4F7B-9039-53C01DE84AFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A85DFB7-409B-4560-B4BB-90FDFEAAAE39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1425" yWindow="1455" windowWidth="11175" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="170">
   <si>
     <t>target_spec</t>
   </si>
@@ -286,6 +286,267 @@
   </si>
   <si>
     <t>When the card destroys another in battle</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>mana_cost/generic</t>
+  </si>
+  <si>
+    <t>mana_cost/red</t>
+  </si>
+  <si>
+    <t>mana_cost/blue</t>
+  </si>
+  <si>
+    <t>mana_cost/green</t>
+  </si>
+  <si>
+    <t>mana_cost/earth</t>
+  </si>
+  <si>
+    <t>mana_cost/white</t>
+  </si>
+  <si>
+    <t>mana_cost/black</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>effects/0</t>
+  </si>
+  <si>
+    <t>background</t>
+  </si>
+  <si>
+    <t>power</t>
+  </si>
+  <si>
+    <t>image</t>
+  </si>
+  <si>
+    <t>toughness</t>
+  </si>
+  <si>
+    <t>Mana_creation</t>
+  </si>
+  <si>
+    <t>range/0</t>
+  </si>
+  <si>
+    <t>range/1</t>
+  </si>
+  <si>
+    <t>range/2</t>
+  </si>
+  <si>
+    <t>range/3</t>
+  </si>
+  <si>
+    <t>range/4</t>
+  </si>
+  <si>
+    <t>effects/0/spec</t>
+  </si>
+  <si>
+    <t>effects/0/target_spec</t>
+  </si>
+  <si>
+    <t>effects/0/trigger_spec</t>
+  </si>
+  <si>
+    <t>effects/0/mandatory</t>
+  </si>
+  <si>
+    <t>effects/0/target_count</t>
+  </si>
+  <si>
+    <t>effects/0/targets</t>
+  </si>
+  <si>
+    <t>effects/0/mana_cost</t>
+  </si>
+  <si>
+    <t>effects/0/once_per_turn</t>
+  </si>
+  <si>
+    <t>effects/0/speed</t>
+  </si>
+  <si>
+    <t>effects/0/description</t>
+  </si>
+  <si>
+    <t>effects/1/spec</t>
+  </si>
+  <si>
+    <t>effects/1/target_spec</t>
+  </si>
+  <si>
+    <t>effects/1/trigger_spec</t>
+  </si>
+  <si>
+    <t>effects/1/target_count</t>
+  </si>
+  <si>
+    <t>effects/1/mandatory</t>
+  </si>
+  <si>
+    <t>effects/1/targets</t>
+  </si>
+  <si>
+    <t>effects/1/mana_cost</t>
+  </si>
+  <si>
+    <t>effects/1/once_per_turn</t>
+  </si>
+  <si>
+    <t>effects/1/speed</t>
+  </si>
+  <si>
+    <t>effects/1/description</t>
+  </si>
+  <si>
+    <t>Fire Elemental</t>
+  </si>
+  <si>
+    <t>Creature</t>
+  </si>
+  <si>
+    <t>red</t>
+  </si>
+  <si>
+    <t>fireElemental.jpg</t>
+  </si>
+  <si>
+    <t>['red','red']</t>
+  </si>
+  <si>
+    <t>2.-1</t>
+  </si>
+  <si>
+    <t>Water Sprite</t>
+  </si>
+  <si>
+    <t>blue</t>
+  </si>
+  <si>
+    <t>waterSprite.jpg</t>
+  </si>
+  <si>
+    <t>['blue','white']</t>
+  </si>
+  <si>
+    <t>1.-1</t>
+  </si>
+  <si>
+    <t>Earth Golem</t>
+  </si>
+  <si>
+    <t>earth</t>
+  </si>
+  <si>
+    <t>Earthgolem.png</t>
+  </si>
+  <si>
+    <t>['earth','earth']</t>
+  </si>
+  <si>
+    <t>Wind Crow</t>
+  </si>
+  <si>
+    <t>green</t>
+  </si>
+  <si>
+    <t>windCrow.jpg</t>
+  </si>
+  <si>
+    <t>['green','green']</t>
+  </si>
+  <si>
+    <t>3.-1</t>
+  </si>
+  <si>
+    <t>Skeleton</t>
+  </si>
+  <si>
+    <t>black</t>
+  </si>
+  <si>
+    <t>skeleton.jpg</t>
+  </si>
+  <si>
+    <t>['black','green']</t>
+  </si>
+  <si>
+    <t>buff self -1/0 instant</t>
+  </si>
+  <si>
+    <t>on_stack_buff</t>
+  </si>
+  <si>
+    <t>soft</t>
+  </si>
+  <si>
+    <t>Loose 1 power</t>
+  </si>
+  <si>
+    <t>Cat Wizard</t>
+  </si>
+  <si>
+    <t>white</t>
+  </si>
+  <si>
+    <t>catwizard.jpg</t>
+  </si>
+  <si>
+    <t>['white','green']</t>
+  </si>
+  <si>
+    <t>buff self +100/0 instant</t>
+  </si>
+  <si>
+    <t>Gain 100 power</t>
+  </si>
+  <si>
+    <t>damage 3</t>
+  </si>
+  <si>
+    <t>Deal 3 damage to target creature</t>
+  </si>
+  <si>
+    <t>Healing potion</t>
+  </si>
+  <si>
+    <t>Spell</t>
+  </si>
+  <si>
+    <t>healingPotion.jpg</t>
+  </si>
+  <si>
+    <t>buff all_creatures +3/+3 until_end_of_turn</t>
+  </si>
+  <si>
+    <t>All creatures gain +3/+3</t>
+  </si>
+  <si>
+    <t>Alik</t>
+  </si>
+  <si>
+    <t>alik.jpg</t>
+  </si>
+  <si>
+    <t>['generic','generic']</t>
+  </si>
+  <si>
+    <t>move_forward</t>
+  </si>
+  <si>
+    <t>Move forward</t>
   </si>
 </sst>
 </file>
@@ -321,8 +582,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -926,7 +1190,7 @@
         <v>24</v>
       </c>
       <c r="D15" t="str">
-        <f t="shared" ref="D15:D23" si="0">UPPER(C15)&amp;","</f>
+        <f t="shared" ref="D15:D21" si="0">UPPER(C15)&amp;","</f>
         <v>ON_MOVE,</v>
       </c>
       <c r="E15" t="s">
@@ -1055,9 +1319,741 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="14.140625" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" style="1" customWidth="1"/>
+    <col min="4" max="9" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:41" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="J1" t="s">
+        <v>92</v>
+      </c>
+      <c r="K1" t="s">
+        <v>93</v>
+      </c>
+      <c r="L1" t="s">
+        <v>94</v>
+      </c>
+      <c r="M1" t="s">
+        <v>95</v>
+      </c>
+      <c r="N1" t="s">
+        <v>96</v>
+      </c>
+      <c r="O1" t="s">
+        <v>97</v>
+      </c>
+      <c r="P1" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>99</v>
+      </c>
+      <c r="R1" t="s">
+        <v>100</v>
+      </c>
+      <c r="S1" t="s">
+        <v>101</v>
+      </c>
+      <c r="T1" t="s">
+        <v>102</v>
+      </c>
+      <c r="U1" t="s">
+        <v>103</v>
+      </c>
+      <c r="V1" t="s">
+        <v>104</v>
+      </c>
+      <c r="W1" t="s">
+        <v>105</v>
+      </c>
+      <c r="X1" t="s">
+        <v>106</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>110</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>112</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>114</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>115</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>116</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>118</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>120</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>121</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>122</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0</v>
+      </c>
+      <c r="J2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L2" t="s">
+        <v>126</v>
+      </c>
+      <c r="M2">
+        <v>40</v>
+      </c>
+      <c r="N2" t="s">
+        <v>127</v>
+      </c>
+      <c r="O2">
+        <v>30</v>
+      </c>
+      <c r="P2" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>2</v>
+      </c>
+      <c r="S2">
+        <v>2.1</v>
+      </c>
+      <c r="T2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" t="s">
+        <v>125</v>
+      </c>
+      <c r="L3" t="s">
+        <v>131</v>
+      </c>
+      <c r="M3">
+        <v>20</v>
+      </c>
+      <c r="N3" t="s">
+        <v>132</v>
+      </c>
+      <c r="O3">
+        <v>40</v>
+      </c>
+      <c r="P3" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>2</v>
+      </c>
+      <c r="S3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="T3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0</v>
+      </c>
+      <c r="J4" t="s">
+        <v>125</v>
+      </c>
+      <c r="L4" t="s">
+        <v>136</v>
+      </c>
+      <c r="M4">
+        <v>10</v>
+      </c>
+      <c r="N4" t="s">
+        <v>137</v>
+      </c>
+      <c r="O4">
+        <v>50</v>
+      </c>
+      <c r="P4" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>2</v>
+      </c>
+      <c r="S4">
+        <v>2.1</v>
+      </c>
+      <c r="T4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" t="s">
+        <v>125</v>
+      </c>
+      <c r="L5" t="s">
+        <v>140</v>
+      </c>
+      <c r="M5">
+        <v>20</v>
+      </c>
+      <c r="N5" t="s">
+        <v>141</v>
+      </c>
+      <c r="O5">
+        <v>20</v>
+      </c>
+      <c r="P5" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>2</v>
+      </c>
+      <c r="S5">
+        <v>3</v>
+      </c>
+      <c r="T5" t="s">
+        <v>143</v>
+      </c>
+      <c r="U5">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
+        <v>125</v>
+      </c>
+      <c r="L6" t="s">
+        <v>145</v>
+      </c>
+      <c r="M6">
+        <v>30</v>
+      </c>
+      <c r="N6" t="s">
+        <v>146</v>
+      </c>
+      <c r="O6">
+        <v>10</v>
+      </c>
+      <c r="P6" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="S6">
+        <v>2</v>
+      </c>
+      <c r="T6" t="s">
+        <v>134</v>
+      </c>
+      <c r="V6" t="s">
+        <v>148</v>
+      </c>
+      <c r="W6" t="s">
+        <v>41</v>
+      </c>
+      <c r="X6" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>1</v>
+      </c>
+      <c r="AA6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>150</v>
+      </c>
+      <c r="AD6">
+        <v>2</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>152</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1</v>
+      </c>
+      <c r="J7" t="s">
+        <v>125</v>
+      </c>
+      <c r="L7" t="s">
+        <v>153</v>
+      </c>
+      <c r="M7">
+        <v>10</v>
+      </c>
+      <c r="N7" t="s">
+        <v>154</v>
+      </c>
+      <c r="O7">
+        <v>30</v>
+      </c>
+      <c r="P7" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>2</v>
+      </c>
+      <c r="S7">
+        <v>3</v>
+      </c>
+      <c r="T7" t="s">
+        <v>143</v>
+      </c>
+      <c r="U7">
+        <v>3.1</v>
+      </c>
+      <c r="V7" t="s">
+        <v>156</v>
+      </c>
+      <c r="W7" t="s">
+        <v>41</v>
+      </c>
+      <c r="X7" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>1</v>
+      </c>
+      <c r="AA7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>150</v>
+      </c>
+      <c r="AD7">
+        <v>1</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>157</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>158</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI7">
+        <v>1</v>
+      </c>
+      <c r="AJ7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>150</v>
+      </c>
+      <c r="AN7">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>160</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" t="s">
+        <v>161</v>
+      </c>
+      <c r="L8" t="s">
+        <v>153</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>162</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8" t="s">
+        <v>155</v>
+      </c>
+      <c r="V8" t="s">
+        <v>163</v>
+      </c>
+      <c r="W8" t="s">
+        <v>1</v>
+      </c>
+      <c r="X8" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>2</v>
+      </c>
+      <c r="AA8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>150</v>
+      </c>
+      <c r="AD8">
+        <v>1</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>165</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" t="s">
+        <v>125</v>
+      </c>
+      <c r="L9" t="s">
+        <v>131</v>
+      </c>
+      <c r="M9">
+        <v>20</v>
+      </c>
+      <c r="N9" t="s">
+        <v>166</v>
+      </c>
+      <c r="O9">
+        <v>30</v>
+      </c>
+      <c r="P9" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>2</v>
+      </c>
+      <c r="S9">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="T9" t="s">
+        <v>134</v>
+      </c>
+      <c r="V9" t="s">
+        <v>168</v>
+      </c>
+      <c r="W9" t="s">
+        <v>41</v>
+      </c>
+      <c r="X9" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z9">
+        <v>1</v>
+      </c>
+      <c r="AA9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>150</v>
+      </c>
+      <c r="AD9">
+        <v>1</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/plan.xlsx
+++ b/plan.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipi\Downloads\mtg\mtg_clone\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arjol\Documents\GitHub\mtg_clone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A85DFB7-409B-4560-B4BB-90FDFEAAAE39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="170">
-  <si>
-    <t>target_spec</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="166">
   <si>
     <t>target_creature</t>
   </si>
@@ -69,9 +65,6 @@
     <t>target_card_in_deck</t>
   </si>
   <si>
-    <t>trigger_spec</t>
-  </si>
-  <si>
     <t>on_play</t>
   </si>
   <si>
@@ -123,9 +116,6 @@
     <t>on_defend</t>
   </si>
   <si>
-    <t>spec</t>
-  </si>
-  <si>
     <t>player</t>
   </si>
   <si>
@@ -276,18 +266,6 @@
     <t>on_turn_end_on_field</t>
   </si>
   <si>
-    <t>when card is attacking</t>
-  </si>
-  <si>
-    <t>when card dies in battle</t>
-  </si>
-  <si>
-    <t>when this card is destroyed from any source</t>
-  </si>
-  <si>
-    <t>When the card destroys another in battle</t>
-  </si>
-  <si>
     <t>id</t>
   </si>
   <si>
@@ -547,13 +525,22 @@
   </si>
   <si>
     <t>Move forward</t>
+  </si>
+  <si>
+    <t>target_spec:</t>
+  </si>
+  <si>
+    <t>trigger_spec:</t>
+  </si>
+  <si>
+    <t>spec:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -931,386 +918,301 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="40.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.5703125" customWidth="1"/>
-    <col min="3" max="3" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="40.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.69921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>163</v>
+      </c>
+      <c r="B1" t="s">
+        <v>164</v>
       </c>
       <c r="C1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="E1" t="s">
+      <c r="C3" t="s">
         <v>28</v>
       </c>
-      <c r="G1" t="s">
+      <c r="D3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2" t="s">
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
         <v>30</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" t="s">
         <v>65</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="C19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" t="s">
         <v>74</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" t="s">
-        <v>79</v>
-      </c>
-      <c r="E5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" t="s">
-        <v>82</v>
-      </c>
-      <c r="E8" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" t="s">
         <v>75</v>
       </c>
-      <c r="C10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" t="s">
-        <v>40</v>
-      </c>
-      <c r="G11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G12" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" t="str">
-        <f>UPPER(C14)&amp;","</f>
-        <v>ON_SUMMON,</v>
-      </c>
-      <c r="E14" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" t="str">
-        <f t="shared" ref="D15:D21" si="0">UPPER(C15)&amp;","</f>
-        <v>ON_MOVE,</v>
-      </c>
-      <c r="E15" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" t="str">
-        <f t="shared" si="0"/>
-        <v>ON_DRAW,</v>
-      </c>
-      <c r="E16" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" t="str">
-        <f t="shared" si="0"/>
-        <v>ON_DEFEND,</v>
-      </c>
-      <c r="E17" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" t="s">
-        <v>64</v>
-      </c>
-      <c r="D18" t="str">
-        <f t="shared" si="0"/>
-        <v>ON_DEATH_ON_FIELD,</v>
-      </c>
-      <c r="E18" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" t="s">
-        <v>68</v>
-      </c>
-      <c r="D19" t="str">
-        <f t="shared" si="0"/>
-        <v>ON_SHIELD_SET,</v>
-      </c>
-      <c r="E19" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20" t="s">
-        <v>72</v>
-      </c>
-      <c r="D20" t="str">
-        <f t="shared" si="0"/>
-        <v>ON_EFFECT_DECLARED,</v>
-      </c>
-      <c r="E20" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" t="s">
-        <v>73</v>
-      </c>
-      <c r="D21" t="str">
-        <f t="shared" si="0"/>
-        <v>ON_EFFECT_ACTIVATED,</v>
-      </c>
-      <c r="E21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>49</v>
-      </c>
-      <c r="C22" t="s">
-        <v>77</v>
-      </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>50</v>
-      </c>
-      <c r="C23" t="s">
-        <v>78</v>
-      </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="I20:I26">
+  <conditionalFormatting sqref="F20:F26">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1318,185 +1220,185 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AO9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="2" max="2" width="14.140625" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" style="1" customWidth="1"/>
-    <col min="4" max="9" width="9.140625" style="1"/>
+    <col min="2" max="2" width="14.09765625" customWidth="1"/>
+    <col min="3" max="3" width="9.59765625" style="1" customWidth="1"/>
+    <col min="4" max="9" width="9.09765625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:41" ht="45">
       <c r="A1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B1" t="s">
+      <c r="I1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="J1" t="s">
         <v>85</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="K1" t="s">
         <v>86</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="L1" t="s">
         <v>87</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="M1" t="s">
         <v>88</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="N1" t="s">
         <v>89</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="O1" t="s">
         <v>90</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="P1" t="s">
         <v>91</v>
       </c>
-      <c r="J1" t="s">
+      <c r="Q1" t="s">
         <v>92</v>
       </c>
-      <c r="K1" t="s">
+      <c r="R1" t="s">
         <v>93</v>
       </c>
-      <c r="L1" t="s">
+      <c r="S1" t="s">
         <v>94</v>
       </c>
-      <c r="M1" t="s">
+      <c r="T1" t="s">
         <v>95</v>
       </c>
-      <c r="N1" t="s">
+      <c r="U1" t="s">
         <v>96</v>
       </c>
-      <c r="O1" t="s">
+      <c r="V1" t="s">
         <v>97</v>
       </c>
-      <c r="P1" t="s">
+      <c r="W1" t="s">
         <v>98</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="X1" t="s">
         <v>99</v>
       </c>
-      <c r="R1" t="s">
+      <c r="Y1" t="s">
         <v>100</v>
       </c>
-      <c r="S1" t="s">
+      <c r="Z1" t="s">
         <v>101</v>
       </c>
-      <c r="T1" t="s">
+      <c r="AA1" t="s">
         <v>102</v>
       </c>
-      <c r="U1" t="s">
+      <c r="AB1" t="s">
         <v>103</v>
       </c>
-      <c r="V1" t="s">
+      <c r="AC1" t="s">
         <v>104</v>
       </c>
-      <c r="W1" t="s">
+      <c r="AD1" t="s">
         <v>105</v>
       </c>
-      <c r="X1" t="s">
+      <c r="AE1" t="s">
         <v>106</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AF1" t="s">
         <v>107</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AG1" t="s">
         <v>108</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AH1" t="s">
         <v>109</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AI1" t="s">
         <v>110</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AJ1" t="s">
         <v>111</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AK1" t="s">
         <v>112</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AL1" t="s">
         <v>113</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AM1" t="s">
         <v>114</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AN1" t="s">
         <v>115</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AO1" t="s">
         <v>116</v>
       </c>
-      <c r="AI1" t="s">
+    </row>
+    <row r="2" spans="1:41" ht="15">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>117</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0</v>
+      </c>
+      <c r="J2" t="s">
         <v>118</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="L2" t="s">
         <v>119</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>121</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>122</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C2" s="1">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1">
-        <v>1</v>
-      </c>
-      <c r="E2" s="1">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1">
-        <v>0</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0</v>
-      </c>
-      <c r="H2" s="1">
-        <v>0</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0</v>
-      </c>
-      <c r="J2" t="s">
-        <v>125</v>
-      </c>
-      <c r="L2" t="s">
-        <v>126</v>
       </c>
       <c r="M2">
         <v>40</v>
       </c>
       <c r="N2" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="O2">
         <v>30</v>
       </c>
       <c r="P2" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="Q2">
         <v>1</v>
@@ -1508,15 +1410,15 @@
         <v>2.1</v>
       </c>
       <c r="T2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:41" ht="15">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C3" s="1">
         <v>0</v>
@@ -1540,22 +1442,22 @@
         <v>0</v>
       </c>
       <c r="J3" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="L3" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="M3">
         <v>20</v>
       </c>
       <c r="N3" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="O3">
         <v>40</v>
       </c>
       <c r="P3" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="Q3">
         <v>1</v>
@@ -1567,15 +1469,15 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="T3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" spans="1:41" ht="15">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="C4" s="1">
         <v>0</v>
@@ -1599,22 +1501,22 @@
         <v>0</v>
       </c>
       <c r="J4" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="L4" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="M4">
         <v>10</v>
       </c>
       <c r="N4" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="O4">
         <v>50</v>
       </c>
       <c r="P4" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="Q4">
         <v>1</v>
@@ -1626,15 +1528,15 @@
         <v>2.1</v>
       </c>
       <c r="T4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:41" ht="15">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C5" s="1">
         <v>0</v>
@@ -1658,22 +1560,22 @@
         <v>0</v>
       </c>
       <c r="J5" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="L5" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="M5">
         <v>20</v>
       </c>
       <c r="N5" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="O5">
         <v>20</v>
       </c>
       <c r="P5" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="Q5">
         <v>1</v>
@@ -1685,18 +1587,18 @@
         <v>3</v>
       </c>
       <c r="T5" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="U5">
         <v>3.1</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:41" ht="15">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C6" s="1">
         <v>0</v>
@@ -1720,22 +1622,22 @@
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="L6" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="M6">
         <v>30</v>
       </c>
       <c r="N6" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="O6">
         <v>10</v>
       </c>
       <c r="P6" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="Q6">
         <v>1</v>
@@ -1747,16 +1649,16 @@
         <v>2</v>
       </c>
       <c r="T6" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="V6" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="W6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="X6" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="Y6" t="b">
         <v>0</v>
@@ -1768,21 +1670,21 @@
         <v>1</v>
       </c>
       <c r="AC6" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="AD6">
         <v>2</v>
       </c>
       <c r="AE6" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="7" spans="1:41" ht="15">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C7" s="1">
         <v>0</v>
@@ -1806,22 +1708,22 @@
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="L7" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="M7">
         <v>10</v>
       </c>
       <c r="N7" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="O7">
         <v>30</v>
       </c>
       <c r="P7" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="Q7">
         <v>1</v>
@@ -1833,19 +1735,19 @@
         <v>3</v>
       </c>
       <c r="T7" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="U7">
         <v>3.1</v>
       </c>
       <c r="V7" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="W7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="X7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y7" t="b">
         <v>0</v>
@@ -1857,22 +1759,22 @@
         <v>1</v>
       </c>
       <c r="AC7" t="s">
+        <v>143</v>
+      </c>
+      <c r="AD7">
+        <v>1</v>
+      </c>
+      <c r="AE7" t="s">
         <v>150</v>
       </c>
-      <c r="AD7">
-        <v>1</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>157</v>
-      </c>
       <c r="AF7" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="AG7" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AI7">
         <v>1</v>
@@ -1884,21 +1786,21 @@
         <v>1</v>
       </c>
       <c r="AM7" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="AN7">
         <v>1</v>
       </c>
       <c r="AO7" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="8" spans="1:41" ht="15">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C8" s="1">
         <v>0</v>
@@ -1922,31 +1824,31 @@
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="L8" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="M8">
         <v>0</v>
       </c>
       <c r="N8" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="V8" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="W8" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="Y8" t="b">
         <v>0</v>
@@ -1958,21 +1860,21 @@
         <v>1</v>
       </c>
       <c r="AC8" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="AD8">
         <v>1</v>
       </c>
       <c r="AE8" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="9" spans="1:41" ht="15">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="C9" s="1">
         <v>1</v>
@@ -1996,22 +1898,22 @@
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="L9" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="M9">
         <v>20</v>
       </c>
       <c r="N9" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="O9">
         <v>30</v>
       </c>
       <c r="P9" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="Q9">
         <v>1</v>
@@ -2023,16 +1925,16 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="T9" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="V9" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="W9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="X9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Y9" t="b">
         <v>1</v>
@@ -2044,13 +1946,13 @@
         <v>0</v>
       </c>
       <c r="AC9" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="AD9">
         <v>1</v>
       </c>
       <c r="AE9" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
